--- a/artfynd/A 44974-2025 artfynd.xlsx
+++ b/artfynd/A 44974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000930</v>
       </c>
       <c r="B2" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44974-2025 artfynd.xlsx
+++ b/artfynd/A 44974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000930</v>
       </c>
       <c r="B2" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44974-2025 artfynd.xlsx
+++ b/artfynd/A 44974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000930</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44974-2025 artfynd.xlsx
+++ b/artfynd/A 44974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000930</v>
       </c>
       <c r="B2" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44974-2025 artfynd.xlsx
+++ b/artfynd/A 44974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000930</v>
       </c>
       <c r="B2" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44974-2025 artfynd.xlsx
+++ b/artfynd/A 44974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000930</v>
       </c>
       <c r="B2" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
